--- a/data/import/polyonics.xlsx
+++ b/data/import/polyonics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U66"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,11 @@
           <t>pub</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -606,6 +611,11 @@
       <c r="U2" t="n">
         <v>1</v>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -690,6 +700,11 @@
       <c r="U3" t="n">
         <v>1</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -774,6 +789,11 @@
       <c r="U4" t="n">
         <v>1</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -858,6 +878,11 @@
       <c r="U5" t="n">
         <v>1</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -942,6 +967,11 @@
       <c r="U6" t="n">
         <v>1</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1026,6 +1056,11 @@
       <c r="U7" t="n">
         <v>1</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1110,6 +1145,11 @@
       <c r="U8" t="n">
         <v>1</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1194,6 +1234,11 @@
       <c r="U9" t="n">
         <v>1</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1278,6 +1323,11 @@
       <c r="U10" t="n">
         <v>1</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1362,6 +1412,11 @@
       <c r="U11" t="n">
         <v>1</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1446,6 +1501,11 @@
       <c r="U12" t="n">
         <v>1</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1530,6 +1590,11 @@
       <c r="U13" t="n">
         <v>1</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1614,6 +1679,11 @@
       <c r="U14" t="n">
         <v>1</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1698,6 +1768,11 @@
       <c r="U15" t="n">
         <v>1</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1782,6 +1857,11 @@
       <c r="U16" t="n">
         <v>1</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1866,6 +1946,11 @@
       <c r="U17" t="n">
         <v>1</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_PCB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1950,6 +2035,11 @@
       <c r="U18" t="n">
         <v>1</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductSheet_Labels_DurableTopcoat.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2034,6 +2124,11 @@
       <c r="U19" t="n">
         <v>1</v>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductSheet_Labels_DurableTopcoat.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2118,6 +2213,11 @@
       <c r="U20" t="n">
         <v>1</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_ESDSafe_Rev0625201.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2202,6 +2302,11 @@
       <c r="U21" t="n">
         <v>1</v>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_ESDSafe_Rev0625201.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2286,6 +2391,11 @@
       <c r="U22" t="n">
         <v>1</v>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_ESDSafe_Rev0625201.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2370,6 +2480,11 @@
       <c r="U23" t="n">
         <v>1</v>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_ESDSafe_Rev0625201.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2454,6 +2569,11 @@
       <c r="U24" t="n">
         <v>1</v>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductSheets_Labels_FlameRetardant.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2538,6 +2658,11 @@
       <c r="U25" t="n">
         <v>1</v>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductSheets_Labels_FlameRetardant.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2625,6 +2750,11 @@
       <c r="U26" t="n">
         <v>1</v>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_CableWireMarking_NylonFR.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2712,6 +2842,11 @@
       <c r="U27" t="n">
         <v>1</v>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Labels_CableWireMarking_NylonFR.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2777,6 +2912,11 @@
       <c r="U28" t="n">
         <v>0</v>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/performancelabels/wire-cable-marking-labels/</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2856,6 +2996,11 @@
       <c r="U29" t="n">
         <v>0</v>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2935,6 +3080,11 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3014,6 +3164,11 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3093,6 +3248,11 @@
       <c r="U32" t="n">
         <v>0</v>
       </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3172,6 +3332,11 @@
       <c r="U33" t="n">
         <v>0</v>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3251,6 +3416,11 @@
       <c r="U34" t="n">
         <v>0</v>
       </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3324,6 +3494,11 @@
       <c r="U35" t="n">
         <v>0</v>
       </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3403,6 +3578,11 @@
       <c r="U36" t="n">
         <v>0</v>
       </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3482,6 +3662,11 @@
       <c r="U37" t="n">
         <v>0</v>
       </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3561,6 +3746,11 @@
       <c r="U38" t="n">
         <v>0</v>
       </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3640,6 +3830,11 @@
       <c r="U39" t="n">
         <v>0</v>
       </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3713,6 +3908,11 @@
       <c r="U40" t="n">
         <v>0</v>
       </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3792,6 +3992,11 @@
       <c r="U41" t="n">
         <v>0</v>
       </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3871,6 +4076,11 @@
       <c r="U42" t="n">
         <v>0</v>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_FlexibleSubstrates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3953,6 +4163,11 @@
       <c r="U43" t="n">
         <v>1</v>
       </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Tapes.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4035,6 +4250,11 @@
       <c r="U44" t="n">
         <v>1</v>
       </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Tapes.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4117,6 +4337,11 @@
       <c r="U45" t="n">
         <v>1</v>
       </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Tapes.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4199,6 +4424,11 @@
       <c r="U46" t="n">
         <v>1</v>
       </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Tapes.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4281,6 +4511,11 @@
       <c r="U47" t="n">
         <v>1</v>
       </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Tapes.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4368,6 +4603,11 @@
       <c r="U48" t="n">
         <v>1</v>
       </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Tapes.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4455,6 +4695,11 @@
       <c r="U49" t="n">
         <v>1</v>
       </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductBrochure_Tapes.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4539,6 +4784,11 @@
       <c r="U50" t="n">
         <v>1</v>
       </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductSheet_Labels_Overlaminates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4623,6 +4873,11 @@
       <c r="U51" t="n">
         <v>1</v>
       </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductSheet_Labels_Overlaminates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4707,6 +4962,11 @@
       <c r="U52" t="n">
         <v>1</v>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/wp-content/uploads/2024/12/ProductSheet_Labels_Overlaminates.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4791,6 +5051,11 @@
       <c r="U53" t="n">
         <v>1</v>
       </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4875,6 +5140,11 @@
       <c r="U54" t="n">
         <v>1</v>
       </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4959,6 +5229,11 @@
       <c r="U55" t="n">
         <v>1</v>
       </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5043,6 +5318,11 @@
       <c r="U56" t="n">
         <v>1</v>
       </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5127,6 +5407,11 @@
       <c r="U57" t="n">
         <v>1</v>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5211,6 +5496,11 @@
       <c r="U58" t="n">
         <v>1</v>
       </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5287,6 +5577,11 @@
       <c r="U59" t="n">
         <v>0</v>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5363,6 +5658,11 @@
       <c r="U60" t="n">
         <v>0</v>
       </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5434,6 +5734,11 @@
       <c r="U61" t="n">
         <v>0</v>
       </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highperformancelabels/</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5504,6 +5809,11 @@
       <c r="U62" t="n">
         <v>0</v>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/industries/aerospace-avionics/</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5559,6 +5869,11 @@
       <c r="U63" t="n">
         <v>0</v>
       </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highdegree/labels/</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5614,6 +5929,11 @@
       <c r="U64" t="n">
         <v>0</v>
       </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highdegree/labels/</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5669,6 +5989,11 @@
       <c r="U65" t="n">
         <v>0</v>
       </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highdegree/tag/</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5723,6 +6048,11 @@
       </c>
       <c r="U66" t="n">
         <v>0</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>https://polyonics.com/highdegree/tag/</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/import/polyonics.xlsx
+++ b/data/import/polyonics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V66"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>tds</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
